--- a/backend/product_database/空調負荷基準表.xlsx
+++ b/backend/product_database/空調負荷基準表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flitt\.gemini\antigravity\scratch\ac-selection-system\backend\product_database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5F36B2-904E-46F7-A5A2-27935E2C85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7522A7-8E95-4C9E-A26A-9595F29ECE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3384" yWindow="564" windowWidth="14568" windowHeight="12060" activeTab="3" xr2:uid="{25F847D7-E8AD-4FFB-BAB5-C066C5856460}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{25F847D7-E8AD-4FFB-BAB5-C066C5856460}"/>
   </bookViews>
   <sheets>
     <sheet name="總表" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>序號</t>
   </si>
@@ -338,6 +338,30 @@
       </rPr>
       <t>、衣帽</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>儲藏,更衣,更衣間,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Microsoft JhengHei UI"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>衣帽</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小辦公, 辦公,洽談, 會議,會客,演講,合約,休息,貴賓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>男廁,女廁,殘障廁所,無障礙</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1527,11 +1551,257 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15D5FA3B-0600-443D-BFA9-48E57479AD3A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="30.44140625" customWidth="1"/>
+    <col min="3" max="3" width="8.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="78" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="5">
+        <v>630</v>
+      </c>
+      <c r="C2" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="5">
+        <v>650</v>
+      </c>
+      <c r="C3" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="5">
+        <v>550</v>
+      </c>
+      <c r="C4" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="5">
+        <v>450</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="5">
+        <v>400</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="5">
+        <v>700</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="5">
+        <v>660</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="5">
+        <v>450</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="5">
+        <v>450</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="H10" s="3"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
